--- a/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1273.81</v>
+        <v>1267.27</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>420.45</v>
+        <v>418.29</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1309.91</v>
+        <v>1303.18</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>389.78</v>
+        <v>385.44</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>572.3</v>
+        <v>569.17</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>150.02</v>
+        <v>149.83</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>679.13</v>
+        <v>681.55</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>108.66</v>
+        <v>109.05</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>64.47</v>
+        <v>65.17</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>868.63</v>
+        <v>871.48</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1948.36</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>724.41</v>
+        <v>729.42</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>75.02</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1114.08</v>
+        <v>1119.27</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>289.33</v>
+        <v>288.82</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>319.36</v>
+        <v>318.87</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>111.28</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>356.1</v>
+        <v>358.61</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>371.36</v>
+        <v>373.98</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>65.15000000000001</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>737.77</v>
+        <v>730.4299999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1278.21</v>
+        <v>1265.49</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>699.61</v>
+        <v>697.1</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>367.66</v>
+        <v>366.86</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>968.74</v>
+        <v>964.67</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2573.74</v>
+        <v>2562.95</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>108.62</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4211.99</v>
+        <v>4208.61</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>102.77</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>714.91</v>
+        <v>718.15</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1102.76</v>
+        <v>1110.35</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>708.6799999999999</v>
+        <v>714.73</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>894.48</v>
+        <v>904.0700000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>477.99</v>
+        <v>483.87</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>706.6</v>
+        <v>715.6799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>706.6</v>
+        <v>715.6799999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1409.48</v>
+        <v>1406.7</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>751.72</v>
+        <v>750.24</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>122.15</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>13238.57</v>
+        <v>13238.66</v>
       </c>
     </row>
     <row r="42">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>187.93</v>
+        <v>188.19</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>234.91</v>
+        <v>235.24</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>147.76</v>
+        <v>148.73</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>738.8</v>
+        <v>756.76</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>616.28</v>
+        <v>618.85</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>767.55</v>
+        <v>761.8</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1151.32</v>
+        <v>1142.7</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>79.22</v>
+        <v>78.89</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>731.1</v>
+        <v>737.75</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>137.08</v>
+        <v>138.04</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2931.72</v>
+        <v>2926.7</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>491.45</v>
+        <v>488.77</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>726.6799999999999</v>
+        <v>722.73</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>408.76</v>
+        <v>407.18</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>158.96</v>
+        <v>158.35</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>468.35</v>
+        <v>466.55</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>66.91</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>690.54</v>
+        <v>721.04</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>717.75</v>
+        <v>719.51</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1149.6</v>
+        <v>1144.46</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>295.19</v>
+        <v>293.87</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>334.55</v>
+        <v>333.05</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>697.0599999999999</v>
+        <v>697.66</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>459.05</v>
+        <v>460.95</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>330.2</v>
+        <v>329.29</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>109.66</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>791.61</v>
+        <v>787.0700000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>987.3200000000001</v>
+        <v>980.99</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>730.3</v>
+        <v>725.62</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>109.55</v>
+        <v>109.07</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>189.65</v>
+        <v>185.57</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>927.73</v>
+        <v>898.15</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>161.89</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>691.29</v>
+        <v>669.25</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1382.59</v>
+        <v>1338.5</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>136.1</v>
+        <v>131.76</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>148.44</v>
+        <v>145.51</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>137.73</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>401.71</v>
+        <v>391.13</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>114.77</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>918.1900000000001</v>
+        <v>901.54</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>350.71</v>
+        <v>341.32</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>670.62</v>
+        <v>672.5700000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1463.17</v>
+        <v>1469.25</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>298.2</v>
+        <v>305.54</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>890.63</v>
+        <v>912.54</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>278.34</v>
+        <v>283.61</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>824.89</v>
+        <v>830.16</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>86.11</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>172.22</v>
+        <v>171.48</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>335.67</v>
+        <v>333.66</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>966.28</v>
+        <v>960.49</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>979.96</v>
+        <v>990.92</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1714.93</v>
+        <v>1734.11</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>727.28</v>
+        <v>732.79</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>457.56</v>
+        <v>461.02</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>979.96</v>
+        <v>987.38</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1602.77</v>
+        <v>1608.85</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1068.52</v>
+        <v>1065.82</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>969.35</v>
+        <v>966.96</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>908.77</v>
+        <v>906.52</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>193.87</v>
+        <v>194.82</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>121.17</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>642.97</v>
+        <v>645.1</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>276.27</v>
+        <v>277.14</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>954.76</v>
+        <v>968.42</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>160.09</v>
+        <v>161.96</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>216.59</v>
+        <v>219.13</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>80.04000000000001</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>960.6799999999999</v>
+        <v>970.45</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>904.17</v>
+        <v>913.37</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>198.21</v>
+        <v>196.71</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>108.02</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>316.01</v>
+        <v>310.67</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1387.08</v>
+        <v>1363.65</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>673.39</v>
+        <v>663.83</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>132.47</v>
+        <v>130.65</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>202.95</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>225.57</v>
+        <v>224.17</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>117.44</v>
+        <v>116.71</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>22.79</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>880.99</v>
+        <v>884.99</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>23.09</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1143.16</v>
+        <v>1160.18</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>50239.58</v>
+        <v>50586.44</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>719.29</v>
+        <v>724.26</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3246.8</v>
+        <v>3269.22</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>859.91</v>
+        <v>848.46</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>644.9299999999999</v>
+        <v>636.34</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>809.8</v>
+        <v>797.8099999999999</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>163.21</v>
+        <v>159.86</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1447.99</v>
+        <v>1461.74</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>211.16</v>
+        <v>213.17</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1460.38</v>
+        <v>1474.25</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>116.14</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>162.71</v>
+        <v>163.35</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>687.1799999999999</v>
+        <v>694.09</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>174.21</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>813.65</v>
+        <v>817.79</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>158.3</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1257.78</v>
+        <v>1262.68</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>104.96</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>141.2</v>
+        <v>140.48</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>793.53</v>
+        <v>789.51</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>168.42</v>
+        <v>169.55</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>793.53</v>
+        <v>798.84</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>566.5700000000001</v>
+        <v>564.78</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1487.23</v>
+        <v>1484.25</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>653.03</v>
+        <v>651.72</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>630.8099999999999</v>
+        <v>629.55</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>223.05</v>
+        <v>221.76</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1357.36</v>
+        <v>1335.6</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>351.87</v>
+        <v>346.23</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>853.86</v>
+        <v>840.17</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>85.67</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>805.8</v>
+        <v>796.42</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>120.87</v>
+        <v>120.2</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>540.6900000000001</v>
+        <v>537.7</v>
       </c>
     </row>
     <row r="162">
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>302.18</v>
+        <v>300.5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1376-521-CM26</t>
+          <t>3281-59-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>100.73</v>
+        <v>255.74</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3281-59-CM26</t>
+          <t>1376-521-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,7 +10451,68 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>257</v>
+        <v>100.23</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1376-551-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>770.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>778993-194-CM25</t>
+          <t>1079486-96-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1267.27</v>
+        <v>871.5700000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>778993-195-CM25</t>
+          <t>1079486-97-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>418.29</v>
+        <v>708.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1079486-159-CM25</t>
+          <t>1554-1476-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1303.18</v>
+        <v>1208.93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3175-118-CM25</t>
+          <t>707416-76-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>385.44</v>
+        <v>238.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1028871-1445-CM25</t>
+          <t>3175-112-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>569.17</v>
+        <v>184.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1028871-1452-CM25</t>
+          <t>1079486-159-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>149.83</v>
+        <v>1303.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3175-132-CM25</t>
+          <t>778993-194-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>681.55</v>
+        <v>1267.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>707416-139-CM25</t>
+          <t>778993-195-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>109.05</v>
+        <v>418.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1176812-180-CM25</t>
+          <t>3175-118-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>65.17</v>
+        <v>385.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>994-9217-CM25</t>
+          <t>1028871-1445-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>871.48</v>
+        <v>569.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1558-311-CM25</t>
+          <t>1028871-1452-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1982</v>
+        <v>149.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1376-893-CM25</t>
+          <t>3175-132-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>729.42</v>
+        <v>681.55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1028871-1469-CM25</t>
+          <t>707416-139-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>75.37</v>
+        <v>109.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1554-1911-CM25</t>
+          <t>1176812-180-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1119.27</v>
+        <v>65.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1088-168-CM25</t>
+          <t>994-9217-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>288.82</v>
+        <v>871.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079486-170-CM25</t>
+          <t>1558-311-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>318.87</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1376-922-CM25</t>
+          <t>1376-893-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>112.07</v>
+        <v>729.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1376-923-CM25</t>
+          <t>1028871-1469-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>358.61</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1346283-262-CM25</t>
+          <t>1554-1911-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>373.98</v>
+        <v>1119.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1671-7800-CM25</t>
+          <t>1088-168-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>64.31999999999999</v>
+        <v>288.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1376-933-CM25</t>
+          <t>1079486-170-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>730.4299999999999</v>
+        <v>318.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>651-261-CM25</t>
+          <t>1376-922-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1265.49</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1079486-178-CM25</t>
+          <t>1376-923-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>697.1</v>
+        <v>358.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>778993-210-CM25</t>
+          <t>1346283-262-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>366.86</v>
+        <v>373.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>778993-208-CM25</t>
+          <t>1671-7800-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>964.67</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>707416-162-CM25</t>
+          <t>1376-933-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2562.95</v>
+        <v>730.4299999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1088-192-CM25</t>
+          <t>651-261-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>107.7</v>
+        <v>1265.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>846-343-CM25</t>
+          <t>1079486-178-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4208.61</v>
+        <v>697.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1376-976-CM25</t>
+          <t>778993-210-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>103.23</v>
+        <v>366.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1376-973-CM25</t>
+          <t>778993-208-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>718.15</v>
+        <v>964.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1554-2090-CM25</t>
+          <t>707416-162-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1110.35</v>
+        <v>2562.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1376-1008-CM25</t>
+          <t>1088-192-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>714.73</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1376-1016-CM25</t>
+          <t>846-343-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>904.0700000000001</v>
+        <v>4208.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2381-1997-CM25</t>
+          <t>1376-973-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>483.87</v>
+        <v>718.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1376-1023-CM25</t>
+          <t>1376-976-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>715.6799999999999</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1376-1024-CM25</t>
+          <t>1554-2090-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>715.6799999999999</v>
+        <v>1110.35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1376-16-CM26</t>
+          <t>1376-1008-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1406.7</v>
+        <v>714.73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1376-15-CM26</t>
+          <t>1376-1016-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>750.24</v>
+        <v>904.0700000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1376-18-CM26</t>
+          <t>2381-1997-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>122.16</v>
+        <v>483.87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1079486-2-CM26</t>
+          <t>1376-1023-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>13238.66</v>
+        <v>715.6799999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1376-17-CM26</t>
+          <t>1376-1024-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>281.9</v>
+        <v>715.6799999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3175-2-CM26</t>
+          <t>1376-16-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>188.19</v>
+        <v>1406.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1376-34-CM26</t>
+          <t>1376-15-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>235.24</v>
+        <v>750.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1556-19-CM26</t>
+          <t>1376-17-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>148.73</v>
+        <v>281.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1376-57-CM26</t>
+          <t>1376-18-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>756.76</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3175-14-CM26</t>
+          <t>1079486-2-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>618.85</v>
+        <v>13238.66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1346283-13-CM26</t>
+          <t>3175-2-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>761.8</v>
+        <v>188.19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1554-164-CM26</t>
+          <t>1376-34-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1142.7</v>
+        <v>235.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1028871-81-CM26</t>
+          <t>1556-19-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>78.89</v>
+        <v>148.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1376-79-CM26</t>
+          <t>1376-57-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>737.75</v>
+        <v>756.76</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1376-82-CM26</t>
+          <t>3175-14-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>138.04</v>
+        <v>618.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3703-114-CM26</t>
+          <t>1554-164-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2926.7</v>
+        <v>1142.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2381-223-CM26</t>
+          <t>1346283-13-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>488.77</v>
+        <v>761.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1376-99-CM26</t>
+          <t>1028871-81-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>722.73</v>
+        <v>78.89</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1376-103-CM26</t>
+          <t>1376-79-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>407.18</v>
+        <v>737.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1376-104-CM26</t>
+          <t>1376-82-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>158.35</v>
+        <v>138.04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079486-14-CM26</t>
+          <t>3703-114-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>466.55</v>
+        <v>2926.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1028871-153-CM26</t>
+          <t>2381-223-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>66.65000000000001</v>
+        <v>488.77</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1376-110-CM26</t>
+          <t>1376-99-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>721.04</v>
+        <v>722.73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1376-129-CM26</t>
+          <t>1079486-14-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>719.51</v>
+        <v>466.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1554-401-CM26</t>
+          <t>1376-103-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1144.46</v>
+        <v>407.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>233-6-CM26</t>
+          <t>1376-104-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>293.87</v>
+        <v>158.35</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3281-30-CM26</t>
+          <t>1028871-153-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>333.05</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1079486-31-CM26</t>
+          <t>1376-110-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>697.66</v>
+        <v>721.04</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1171166-95-CM26</t>
+          <t>1376-129-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>460.95</v>
+        <v>719.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>994-44-CM26</t>
+          <t>233-6-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>329.29</v>
+        <v>293.87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>952751-57-CM26</t>
+          <t>3281-30-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>108.4</v>
+        <v>333.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>778993-23-CM26</t>
+          <t>1554-401-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>787.0700000000001</v>
+        <v>1144.46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1376-179-CM26</t>
+          <t>1079486-31-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>980.99</v>
+        <v>697.66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1376-181-CM26</t>
+          <t>1171166-95-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>725.62</v>
+        <v>460.95</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1088-23-CM26</t>
+          <t>994-44-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>109.07</v>
+        <v>329.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>949-11-CM26</t>
+          <t>952751-57-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.901.005-3</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Mineduc Administración III Región</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>185.57</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1028871-224-CM26</t>
+          <t>778993-23-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>898.15</v>
+        <v>787.0700000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3175-43-CM26</t>
+          <t>1376-181-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>156.73</v>
+        <v>725.62</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>952751-81-CM26</t>
+          <t>1376-179-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5038,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>669.25</v>
+        <v>980.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>952751-82-CM26</t>
+          <t>1088-23-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5099,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1338.5</v>
+        <v>109.07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>952751-83-CM26</t>
+          <t>949-11-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>60.901.005-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>Mineduc Administración III Región</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>131.76</v>
+        <v>185.57</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1556-94-CM26</t>
+          <t>3175-43-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>145.51</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1376-215-CM26</t>
+          <t>952751-81-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>134.1</v>
+        <v>669.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1376-213-CM26</t>
+          <t>952751-82-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>391.13</v>
+        <v>1338.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1376-219-CM26</t>
+          <t>952751-83-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>111.75</v>
+        <v>131.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1376-220-CM26</t>
+          <t>1028871-224-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>901.54</v>
+        <v>898.15</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>952751-86-CM26</t>
+          <t>1556-94-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,22 +5531,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>341.32</v>
+        <v>145.51</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2381-436-CM26</t>
+          <t>1376-219-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>672.5700000000001</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1554-661-CM26</t>
+          <t>1376-215-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1469.25</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1171166-129-CM26</t>
+          <t>1376-213-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>305.54</v>
+        <v>391.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1376-234-CM26</t>
+          <t>1376-220-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>912.54</v>
+        <v>901.54</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1088-29-CM26</t>
+          <t>952751-86-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>283.61</v>
+        <v>341.32</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>952751-101-CM26</t>
+          <t>2381-436-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>830.16</v>
+        <v>672.5700000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1028871-290-CM26</t>
+          <t>1554-661-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>86.29000000000001</v>
+        <v>1469.25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1028871-291-CM26</t>
+          <t>1171166-129-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>171.48</v>
+        <v>305.54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1376-265-CM26</t>
+          <t>1376-234-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>333.66</v>
+        <v>912.54</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1176812-56-CM26</t>
+          <t>1088-29-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>960.49</v>
+        <v>283.61</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1376-280-CM26</t>
+          <t>952751-101-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,27 +6197,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>990.92</v>
+        <v>830.16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1376-281-CM26</t>
+          <t>1028871-290-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1734.11</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3175-56-CM26</t>
+          <t>1028871-291-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>732.79</v>
+        <v>171.48</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>233-13-CM26</t>
+          <t>1376-265-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>461.02</v>
+        <v>333.66</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1376-283-CM26</t>
+          <t>1176812-56-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>987.38</v>
+        <v>960.49</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1554-825-CM26</t>
+          <t>1376-280-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1608.85</v>
+        <v>990.92</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1346283-127-CM26</t>
+          <t>1376-281-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1065.82</v>
+        <v>1734.11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1376-338-CM26</t>
+          <t>3175-56-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,22 +6629,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>966.96</v>
+        <v>732.79</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1376-337-CM26</t>
+          <t>233-13-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>906.52</v>
+        <v>461.02</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3175-64-CM26</t>
+          <t>1376-283-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>194.82</v>
+        <v>987.38</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1376-344-CM26</t>
+          <t>1554-825-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,22 +6812,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>121.76</v>
+        <v>1608.85</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2381-639-CM26</t>
+          <t>1346283-127-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,22 +6873,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>645.1</v>
+        <v>1065.82</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1552-223-CM26</t>
+          <t>1376-338-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>277.14</v>
+        <v>966.96</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1376-366-CM26</t>
+          <t>1376-337-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>968.42</v>
+        <v>906.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1028871-342-CM26</t>
+          <t>3175-64-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>161.96</v>
+        <v>194.82</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>873-20-CM26</t>
+          <t>1376-344-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,27 +7112,27 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>219.13</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1028871-341-CM26</t>
+          <t>2381-639-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,27 +7173,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>80.98</v>
+        <v>645.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>952751-140-CM26</t>
+          <t>1552-223-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7234,27 +7234,27 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>970.45</v>
+        <v>277.14</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>952751-139-CM26</t>
+          <t>1376-366-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>913.37</v>
+        <v>968.42</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1376-381-CM26</t>
+          <t>873-20-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>196.71</v>
+        <v>219.13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1376-383-CM26</t>
+          <t>1028871-341-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>107.2</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>751-201-CM26</t>
+          <t>1028871-342-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>310.67</v>
+        <v>161.96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1554-988-CM26</t>
+          <t>952751-140-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +7544,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1363.65</v>
+        <v>970.45</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5350-1018-CM26</t>
+          <t>952751-139-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>663.83</v>
+        <v>913.37</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2579-22-CM26</t>
+          <t>1376-381-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>130.65</v>
+        <v>196.71</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>778993-70-CM26</t>
+          <t>1376-383-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>200.16</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1028871-364-CM26</t>
+          <t>751-201-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>224.17</v>
+        <v>310.67</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1171166-199-CM26</t>
+          <t>1554-988-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,22 +7849,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>116.71</v>
+        <v>1363.65</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1671-114-CM26</t>
+          <t>5350-1018-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,22 +7910,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>22.89</v>
+        <v>663.83</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1376-391-CM26</t>
+          <t>2579-22-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>884.99</v>
+        <v>130.65</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1796-28-CM26</t>
+          <t>778993-70-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,22 +8032,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>23.44</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1376-408-CM26</t>
+          <t>1171166-199-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1160.18</v>
+        <v>116.71</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2322-439-CM26</t>
+          <t>1028871-364-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>50586.44</v>
+        <v>224.17</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>952751-155-CM26</t>
+          <t>1671-114-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,22 +8215,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>724.26</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>952751-157-CM26</t>
+          <t>1376-391-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,22 +8276,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3269.22</v>
+        <v>884.99</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1376-433-CM26</t>
+          <t>1796-28-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,22 +8337,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>848.46</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1376-434-CM26</t>
+          <t>1376-408-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>636.34</v>
+        <v>1160.18</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1079486-125-CM26</t>
+          <t>2322-439-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>797.8099999999999</v>
+        <v>50586.44</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1376-444-CM26</t>
+          <t>952751-155-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>159.86</v>
+        <v>724.26</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>778993-92-CM26</t>
+          <t>952751-157-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8576,27 +8576,27 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1461.74</v>
+        <v>3269.22</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1376-448-CM26</t>
+          <t>1376-433-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>213.17</v>
+        <v>848.46</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>952751-174-CM26</t>
+          <t>1376-434-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8698,27 +8698,27 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1474.25</v>
+        <v>636.34</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1376-447-CM26</t>
+          <t>1079486-125-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>116.59</v>
+        <v>797.8099999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>810406-107-CM26</t>
+          <t>1376-444-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8820,27 +8820,27 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>163.35</v>
+        <v>159.86</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>952751-175-CM26</t>
+          <t>952751-174-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>694.09</v>
+        <v>1474.25</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3175-81-CM26</t>
+          <t>1376-448-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,22 +8947,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>175.96</v>
+        <v>213.17</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1028871-408-CM26</t>
+          <t>778993-92-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>71.31</v>
+        <v>1461.74</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>778993-91-CM26</t>
+          <t>1376-447-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>817.79</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1556-185-CM26</t>
+          <t>810406-107-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>159.1</v>
+        <v>163.35</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1554-1132-CM26</t>
+          <t>952751-175-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1262.68</v>
+        <v>694.09</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1079486-137-CM26</t>
+          <t>3175-81-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,22 +9252,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>104.42</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1028871-419-CM26</t>
+          <t>1028871-408-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>140.48</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1376-459-CM26</t>
+          <t>778993-91-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>789.51</v>
+        <v>817.79</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1176812-64-CM26</t>
+          <t>1556-185-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>169.55</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1376-470-CM26</t>
+          <t>1554-1132-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,22 +9496,22 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>798.84</v>
+        <v>1262.68</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1376-482-CM26</t>
+          <t>1376-459-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>564.78</v>
+        <v>789.51</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3175-88-CM26</t>
+          <t>1079486-137-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1484.25</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>233-38-CM26</t>
+          <t>1028871-419-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>651.72</v>
+        <v>140.48</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1026-42-CM26</t>
+          <t>1176812-64-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,22 +9740,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>629.55</v>
+        <v>169.55</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>411-325-CM26</t>
+          <t>1376-470-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,22 +9801,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>221.76</v>
+        <v>798.84</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>952751-215-CM26</t>
+          <t>1376-482-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1335.6</v>
+        <v>564.78</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>952751-216-CM26</t>
+          <t>1026-42-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>346.23</v>
+        <v>629.55</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1346283-197-CM26</t>
+          <t>3175-88-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>GOBERNACION MARITIMA DE CALDERA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>840.17</v>
+        <v>1484.25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>904-117-CM26</t>
+          <t>233-38-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>84.67</v>
+        <v>651.72</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1376-517-CM26</t>
+          <t>411-325-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10106,22 +10106,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>796.42</v>
+        <v>221.76</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1376-519-CM26</t>
+          <t>952751-216-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>120.2</v>
+        <v>346.23</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2381-902-CM26</t>
+          <t>952751-215-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>537.7</v>
+        <v>1335.6</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1376-520-CM26</t>
+          <t>1346283-197-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,22 +10289,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>300.5</v>
+        <v>840.17</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3281-59-CM26</t>
+          <t>904-117-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>255.74</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1376-521-CM26</t>
+          <t>1376-517-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>100.23</v>
+        <v>796.42</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1376-551-CM26</t>
+          <t>2381-902-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10467,27 +10467,27 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,6 +10512,311 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
+        <v>537.7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1376-519-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>120.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1376-520-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>300.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>3281-59-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>255.74</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1376-521-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>100.23</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1376-551-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
         <v>770.42</v>
       </c>
     </row>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M248"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3281-53-CM25</t>
+          <t>846-232-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>116.8</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>846-232-CM25</t>
+          <t>3281-53-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>91.7</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1028871-1097-CM25</t>
+          <t>1028871-1099-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>19.97</v>
+        <v>152.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1028871-1099-CM25</t>
+          <t>1028871-1100-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>152.88</v>
+        <v>76.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1028871-1100-CM25</t>
+          <t>1028871-1102-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>76.44</v>
+        <v>152.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1028871-1102-CM25</t>
+          <t>1028871-1103-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1028871-1103-CM25</t>
+          <t>1028871-1097-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>152.88</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="14">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2380-1550-CM25</t>
+          <t>1376-552-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>222.06</v>
+        <v>494.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>949-73-CM25</t>
+          <t>1376-554-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.901.005-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>159.83</v>
+        <v>391.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1376-554-CM25</t>
+          <t>2380-1550-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>391.3</v>
+        <v>222.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1376-552-CM25</t>
+          <t>949-73-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.901.005-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>494.13</v>
+        <v>159.83</v>
       </c>
     </row>
     <row r="20">
@@ -1917,7 +1917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>233-58-CM25</t>
+          <t>1554-1476-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>649.24</v>
+        <v>1208.93</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1554-1476-CM25</t>
+          <t>233-58-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1208.93</v>
+        <v>649.24</v>
       </c>
     </row>
     <row r="27">
@@ -3625,7 +3625,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1376-732-CM25</t>
+          <t>1376-731-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>138.11</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1376-731-CM25</t>
+          <t>1376-732-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>110.49</v>
+        <v>138.11</v>
       </c>
     </row>
     <row r="55">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6126,7 +6126,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1376-922-CM25</t>
+          <t>1376-923-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>112.07</v>
+        <v>358.61</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1376-923-CM25</t>
+          <t>1346283-262-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>358.61</v>
+        <v>373.98</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1346283-262-CM25</t>
+          <t>1376-922-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>373.98</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="97">
@@ -6370,7 +6370,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>651-261-CM25</t>
+          <t>1376-933-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1265.49</v>
+        <v>730.4299999999999</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1376-933-CM25</t>
+          <t>651-261-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>730.4299999999999</v>
+        <v>1265.49</v>
       </c>
     </row>
     <row r="100">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1554-401-CM26</t>
+          <t>233-6-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1144.46</v>
+        <v>293.87</v>
       </c>
     </row>
     <row r="139">
@@ -8932,7 +8932,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>233-6-CM26</t>
+          <t>1554-401-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>293.87</v>
+        <v>1144.46</v>
       </c>
     </row>
     <row r="141">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9176,7 +9176,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>952751-57-CM26</t>
+          <t>778993-23-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>108.4</v>
+        <v>787.0700000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>778993-23-CM26</t>
+          <t>1376-179-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>787.0700000000001</v>
+        <v>980.99</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1376-179-CM26</t>
+          <t>1376-181-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>980.99</v>
+        <v>725.62</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1376-181-CM26</t>
+          <t>1088-23-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>725.62</v>
+        <v>109.07</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1088-23-CM26</t>
+          <t>949-11-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.901.005-3</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>109.07</v>
+        <v>185.57</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>949-11-CM26</t>
+          <t>3175-43-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>60.901.005-3</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Mineduc Administración III Región</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>185.57</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3175-43-CM26</t>
+          <t>1028871-224-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>156.73</v>
+        <v>898.15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>952751-81-CM26</t>
+          <t>1556-94-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>669.25</v>
+        <v>145.51</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>952751-82-CM26</t>
+          <t>1376-213-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,22 +9679,22 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1338.5</v>
+        <v>391.13</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>952751-83-CM26</t>
+          <t>1376-215-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,22 +9740,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>131.76</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1028871-224-CM26</t>
+          <t>1376-219-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>898.15</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1556-94-CM26</t>
+          <t>1376-220-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>145.51</v>
+        <v>901.54</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1376-213-CM26</t>
+          <t>2381-436-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,22 +9923,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>391.13</v>
+        <v>672.5700000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1376-215-CM26</t>
+          <t>1554-661-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>134.1</v>
+        <v>1469.25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1376-219-CM26</t>
+          <t>1376-234-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>111.75</v>
+        <v>912.54</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1376-220-CM26</t>
+          <t>1171166-129-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>901.54</v>
+        <v>305.54</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>952751-86-CM26</t>
+          <t>1088-29-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>341.32</v>
+        <v>283.61</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2381-436-CM26</t>
+          <t>1028871-290-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,22 +10228,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>672.5700000000001</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1554-661-CM26</t>
+          <t>1028871-291-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1469.25</v>
+        <v>171.48</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1171166-129-CM26</t>
+          <t>1376-265-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>305.54</v>
+        <v>333.66</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1376-234-CM26</t>
+          <t>1176812-56-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>912.54</v>
+        <v>960.49</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1088-29-CM26</t>
+          <t>1376-280-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>283.61</v>
+        <v>990.92</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>952751-101-CM26</t>
+          <t>1376-281-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10528,27 +10528,27 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>830.16</v>
+        <v>1734.11</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1028871-290-CM26</t>
+          <t>3175-56-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>86.29000000000001</v>
+        <v>732.79</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1028871-291-CM26</t>
+          <t>233-13-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>171.48</v>
+        <v>461.02</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1376-265-CM26</t>
+          <t>1376-283-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>333.66</v>
+        <v>987.38</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1176812-56-CM26</t>
+          <t>1554-825-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>960.49</v>
+        <v>1608.85</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1376-281-CM26</t>
+          <t>1346283-127-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1734.11</v>
+        <v>1065.82</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1376-280-CM26</t>
+          <t>1376-337-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>990.92</v>
+        <v>906.52</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3175-56-CM26</t>
+          <t>1376-338-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>732.79</v>
+        <v>966.96</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>233-13-CM26</t>
+          <t>1376-344-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11021,22 +11021,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>461.02</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1376-283-CM26</t>
+          <t>3175-64-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>987.38</v>
+        <v>194.82</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1554-825-CM26</t>
+          <t>2381-639-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11143,22 +11143,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1608.85</v>
+        <v>645.1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1346283-127-CM26</t>
+          <t>1552-223-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1065.82</v>
+        <v>277.14</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1376-337-CM26</t>
+          <t>1376-366-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>906.52</v>
+        <v>968.42</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1376-338-CM26</t>
+          <t>873-20-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11321,27 +11321,27 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>966.96</v>
+        <v>219.13</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3175-64-CM26</t>
+          <t>1028871-341-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>194.82</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1376-344-CM26</t>
+          <t>1028871-342-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11443,27 +11443,27 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>121.76</v>
+        <v>161.96</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2381-639-CM26</t>
+          <t>1376-381-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11504,27 +11504,27 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>645.1</v>
+        <v>196.71</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1552-223-CM26</t>
+          <t>1376-383-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>277.14</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1376-366-CM26</t>
+          <t>751-201-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>968.42</v>
+        <v>310.67</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1028871-342-CM26</t>
+          <t>1554-988-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>161.96</v>
+        <v>1363.65</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1028871-341-CM26</t>
+          <t>5350-1018-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,22 +11753,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>80.98</v>
+        <v>663.83</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>873-20-CM26</t>
+          <t>2579-22-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>219.13</v>
+        <v>130.65</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>952751-139-CM26</t>
+          <t>778993-70-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,22 +11875,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>913.37</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>952751-140-CM26</t>
+          <t>1171166-199-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>970.45</v>
+        <v>116.71</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1376-381-CM26</t>
+          <t>1028871-364-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>196.71</v>
+        <v>224.17</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1376-383-CM26</t>
+          <t>1376-391-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>107.2</v>
+        <v>884.99</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>751-201-CM26</t>
+          <t>1671-114-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>310.67</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1554-988-CM26</t>
+          <t>1796-28-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12180,22 +12180,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1363.65</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5350-1018-CM26</t>
+          <t>1376-408-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>663.83</v>
+        <v>1160.18</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2579-22-CM26</t>
+          <t>2322-439-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>130.65</v>
+        <v>50586.44</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>778993-70-CM26</t>
+          <t>1376-433-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>200.16</v>
+        <v>848.46</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1028871-364-CM26</t>
+          <t>1376-434-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>224.17</v>
+        <v>636.34</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1171166-199-CM26</t>
+          <t>1079486-125-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12485,22 +12485,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>116.71</v>
+        <v>797.8099999999999</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1376-391-CM26</t>
+          <t>1376-444-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12546,12 +12546,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>884.99</v>
+        <v>159.86</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1671-114-CM26</t>
+          <t>778993-92-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>22.89</v>
+        <v>1461.74</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1376-408-CM26</t>
+          <t>1376-448-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12663,17 +12663,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1160.18</v>
+        <v>213.17</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1796-28-CM26</t>
+          <t>1376-447-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12724,27 +12724,27 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>23.44</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2322-439-CM26</t>
+          <t>810406-107-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12785,12 +12785,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>50586.44</v>
+        <v>163.35</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>952751-155-CM26</t>
+          <t>1028871-408-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12846,27 +12846,27 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>724.26</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>952751-157-CM26</t>
+          <t>3175-81-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12907,27 +12907,27 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3269.22</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1376-433-CM26</t>
+          <t>778993-91-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>848.46</v>
+        <v>817.79</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1376-434-CM26</t>
+          <t>1556-185-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13044,12 +13044,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>636.34</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1079486-125-CM26</t>
+          <t>1554-1132-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13090,27 +13090,27 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>797.8099999999999</v>
+        <v>1262.68</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1376-444-CM26</t>
+          <t>1079486-137-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13151,27 +13151,27 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>159.86</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>778993-92-CM26</t>
+          <t>1028871-419-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1461.74</v>
+        <v>140.48</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1376-448-CM26</t>
+          <t>1376-459-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>213.17</v>
+        <v>789.51</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>952751-174-CM26</t>
+          <t>1176812-64-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13339,22 +13339,22 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1474.25</v>
+        <v>169.55</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1376-447-CM26</t>
+          <t>1376-470-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>116.59</v>
+        <v>798.84</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>810406-107-CM26</t>
+          <t>1376-482-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>163.35</v>
+        <v>564.78</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>952751-175-CM26</t>
+          <t>1026-42-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>694.09</v>
+        <v>629.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1028871-408-CM26</t>
+          <t>3175-88-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13583,22 +13583,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>71.31</v>
+        <v>1484.25</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3175-81-CM26</t>
+          <t>233-38-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>175.96</v>
+        <v>651.72</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>778993-91-CM26</t>
+          <t>411-325-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13705,22 +13705,22 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>817.79</v>
+        <v>221.76</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1556-185-CM26</t>
+          <t>1346283-197-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>159.1</v>
+        <v>840.17</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1554-1132-CM26</t>
+          <t>1376-517-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13827,22 +13827,22 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1262.68</v>
+        <v>796.42</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1079486-137-CM26</t>
+          <t>904-117-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>104.42</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1028871-419-CM26</t>
+          <t>2381-902-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13949,22 +13949,22 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13989,13 +13989,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>140.48</v>
+        <v>537.7</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1376-459-CM26</t>
+          <t>1376-519-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>789.51</v>
+        <v>120.2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1176812-64-CM26</t>
+          <t>1376-520-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>169.55</v>
+        <v>300.5</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1376-470-CM26</t>
+          <t>1376-521-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>798.84</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1376-482-CM26</t>
+          <t>3281-59-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14193,22 +14193,22 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>564.78</v>
+        <v>255.74</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1026-42-CM26</t>
+          <t>1554-1319-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14249,27 +14249,27 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>629.55</v>
+        <v>1315.87</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3175-88-CM26</t>
+          <t>1376-545-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14310,27 +14310,27 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1484.25</v>
+        <v>206.78</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>233-38-CM26</t>
+          <t>1376-551-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>651.72</v>
+        <v>770.42</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>411-325-CM26</t>
+          <t>846-130-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14432,27 +14432,27 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>221.76</v>
+        <v>191.09</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1346283-197-CM26</t>
+          <t>1376-588-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14493,27 +14493,27 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>840.17</v>
+        <v>1419.14</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>952751-215-CM26</t>
+          <t>1028871-491-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14554,27 +14554,27 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1335.6</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>952751-216-CM26</t>
+          <t>1079486-196-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14615,12 +14615,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>346.23</v>
+        <v>727.1799999999999</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>904-117-CM26</t>
+          <t>1088-99-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14676,12 +14676,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>84.67</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1376-517-CM26</t>
+          <t>3175-104-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>796.42</v>
+        <v>154.4</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2381-902-CM26</t>
+          <t>5350-1375-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>537.7</v>
+        <v>464.89</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1376-519-CM26</t>
+          <t>1376-642-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14904,13 +14904,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>120.2</v>
+        <v>557.87</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1376-520-CM26</t>
+          <t>1171166-224-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14920,12 +14920,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14935,12 +14935,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14950,12 +14950,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -14965,13 +14965,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>300.5</v>
+        <v>194.45</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1376-521-CM26</t>
+          <t>1079486-205-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14981,12 +14981,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14996,12 +14996,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15011,12 +15011,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15026,13 +15026,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>100.23</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3281-59-CM26</t>
+          <t>1376-645-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>255.74</v>
+        <v>279.1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1554-1319-CM26</t>
+          <t>1376-646-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15103,12 +15103,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1315.87</v>
+        <v>130.25</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1376-545-CM26</t>
+          <t>1376-656-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>206.78</v>
+        <v>756.02</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1376-551-CM26</t>
+          <t>1554-1516-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15225,27 +15225,27 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>770.42</v>
+        <v>1188.28</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>846-130-CM26</t>
+          <t>2381-1186-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15286,27 +15286,27 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>191.09</v>
+        <v>509.73</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1376-588-CM26</t>
+          <t>707416-79-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15347,12 +15347,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1419.14</v>
+        <v>123.96</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1028871-491-CM26</t>
+          <t>707416-80-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15408,27 +15408,27 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>70.09</v>
+        <v>159.3</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1088-99-CM26</t>
+          <t>1376-679-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15469,12 +15469,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>109.25</v>
+        <v>101.72</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1079486-196-CM26</t>
+          <t>1079486-217-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15530,17 +15530,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15575,7 +15575,312 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>727.1799999999999</v>
+        <v>100.32</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1028871-584-CM26</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="n">
+        <v>138.72</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1376-705-CM26</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>758.89</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>778993-144-CM26</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>61.946.100-2</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>686.17</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1376-688-CM26</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="n">
+        <v>758.89</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1346283-251-CM26</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="n">
+        <v>782.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M360"/>
+  <dimension ref="A1:M365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1814,7 +1814,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1376-119-CM25</t>
+          <t>3175-22-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1854,17 +1854,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>114.89</v>
+        <v>343.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1376-120-CM25</t>
+          <t>1376-119-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>459.58</v>
+        <v>114.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3175-22-CM25</t>
+          <t>1376-120-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>343.56</v>
+        <v>459.58</v>
       </c>
     </row>
     <row r="25">
@@ -2529,7 +2529,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3281-25-CM25</t>
+          <t>1346283-59-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>234.95</v>
+        <v>1234.85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1346283-59-CM25</t>
+          <t>1376-178-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2634,17 +2634,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1234.85</v>
+        <v>474.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1376-178-CM25</t>
+          <t>1376-179-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>474.8</v>
+        <v>854.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1376-179-CM25</t>
+          <t>3281-25-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>854.63</v>
+        <v>234.95</v>
       </c>
     </row>
     <row r="37">
@@ -4024,7 +4024,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3175-54-CM25</t>
+          <t>1671-83-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4064,17 +4064,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>188.26</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1671-83-CM25</t>
+          <t>3175-54-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4129,17 +4129,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>58.76</v>
+        <v>188.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1376-328-CM25</t>
+          <t>994-126-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>524.01</v>
+        <v>292.23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>994-126-CM25</t>
+          <t>1376-328-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>292.23</v>
+        <v>524.01</v>
       </c>
     </row>
     <row r="60">
@@ -4934,7 +4934,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1376-343-CM25</t>
+          <t>1376-362-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>87.66</v>
+        <v>613.62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1376-362-CM25</t>
+          <t>1376-343-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>613.62</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="72">
@@ -5324,7 +5324,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1079486-60-CM25</t>
+          <t>1026-48-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5344,17 +5344,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>477.87</v>
+        <v>451.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1026-48-CM25</t>
+          <t>1079486-60-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>451.49</v>
+        <v>477.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1376-400-CM25</t>
+          <t>1554-1092-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5494,17 +5494,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>260.63</v>
+        <v>1371.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1554-1092-CM25</t>
+          <t>1376-400-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5559,17 +5559,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1371.54</v>
+        <v>260.63</v>
       </c>
     </row>
     <row r="80">
@@ -5779,7 +5779,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1376-410-CM25</t>
+          <t>846-182-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5819,17 +5819,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>490.83</v>
+        <v>172.78</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>846-182-CM25</t>
+          <t>1376-410-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5884,17 +5884,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>172.78</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="85">
@@ -6234,7 +6234,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1376-456-CM25</t>
+          <t>1376-455-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>325.75</v>
+        <v>488.62</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1376-455-CM25</t>
+          <t>1376-456-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>488.62</v>
+        <v>325.75</v>
       </c>
     </row>
     <row r="92">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3175-75-CM25</t>
+          <t>3175-77-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6469,17 +6469,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>116.61</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3175-77-CM25</t>
+          <t>3175-75-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6534,17 +6534,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>214.4</v>
+        <v>116.61</v>
       </c>
     </row>
     <row r="95">
@@ -7209,7 +7209,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1376-513-CM25</t>
+          <t>1176812-118-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7249,17 +7249,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>76.63</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1176812-119-CM25</t>
+          <t>1376-513-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7314,17 +7314,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>52.22</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1176812-118-CM25</t>
+          <t>1176812-119-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3281-53-CM25</t>
+          <t>846-232-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7834,17 +7834,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>116.8</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>846-232-CM25</t>
+          <t>3281-53-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7899,17 +7899,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>91.7</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1028871-1099-CM25</t>
+          <t>1028871-1103-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1028871-1102-CM25</t>
+          <t>1028871-1097-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8094,17 +8094,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>152.88</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1028871-1103-CM25</t>
+          <t>1028871-1102-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8184,7 +8184,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1028871-1097-CM25</t>
+          <t>1028871-1099-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8224,17 +8224,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>19.97</v>
+        <v>152.88</v>
       </c>
     </row>
     <row r="121">
@@ -8769,7 +8769,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2381-1010-CM25</t>
+          <t>1376-593-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8809,17 +8809,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>510.59</v>
+        <v>471.41</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1376-593-CM25</t>
+          <t>2381-1010-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8874,17 +8874,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>471.41</v>
+        <v>510.59</v>
       </c>
     </row>
     <row r="131">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1376-603-CM25</t>
+          <t>1376-602-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>103.93</v>
+        <v>236.22</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1376-602-CM25</t>
+          <t>1376-603-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>236.22</v>
+        <v>103.93</v>
       </c>
     </row>
     <row r="136">
@@ -10329,7 +10329,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1171166-364-CM25</t>
+          <t>1554-1594-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>235.1</v>
+        <v>1179.21</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1554-1594-CM25</t>
+          <t>1171166-364-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1179.21</v>
+        <v>235.1</v>
       </c>
     </row>
     <row r="155">
@@ -10784,7 +10784,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1376-732-CM25</t>
+          <t>1376-731-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>138.11</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1376-731-CM25</t>
+          <t>1376-732-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10908,7 +10908,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>110.49</v>
+        <v>138.11</v>
       </c>
     </row>
     <row r="162">
@@ -11694,7 +11694,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3175-112-CM25</t>
+          <t>1376-789-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>184.08</v>
+        <v>744.25</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1376-789-CM25</t>
+          <t>3175-112-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>744.25</v>
+        <v>184.08</v>
       </c>
     </row>
     <row r="176">
@@ -13449,7 +13449,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1376-922-CM25</t>
+          <t>1376-923-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13508,13 +13508,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>112.07</v>
+        <v>358.61</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1376-923-CM25</t>
+          <t>1376-922-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13573,7 +13573,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>358.61</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="203">
@@ -15789,7 +15789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2381-223-CM26</t>
+          <t>1376-99-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15809,17 +15809,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15829,17 +15829,17 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>488.77</v>
+        <v>722.73</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1376-99-CM26</t>
+          <t>2381-223-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15874,17 +15874,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15894,17 +15894,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -15913,7 +15913,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>722.73</v>
+        <v>488.77</v>
       </c>
     </row>
     <row r="239">
@@ -17024,7 +17024,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3175-43-CM26</t>
+          <t>1028871-224-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>156.73</v>
+        <v>898.15</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1028871-224-CM26</t>
+          <t>3175-43-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>898.15</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="258">
@@ -17219,7 +17219,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1376-213-CM26</t>
+          <t>1376-215-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>391.13</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1376-215-CM26</t>
+          <t>1376-219-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>134.1</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1376-219-CM26</t>
+          <t>1376-213-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17408,7 +17408,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>111.75</v>
+        <v>391.13</v>
       </c>
     </row>
     <row r="262">
@@ -17609,7 +17609,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1171166-129-CM26</t>
+          <t>1376-234-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17649,17 +17649,17 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -17668,13 +17668,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>305.54</v>
+        <v>912.54</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1376-234-CM26</t>
+          <t>1171166-129-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17699,12 +17699,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17714,17 +17714,17 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -17733,7 +17733,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>912.54</v>
+        <v>305.54</v>
       </c>
     </row>
     <row r="267">
@@ -17934,7 +17934,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1376-265-CM26</t>
+          <t>1176812-56-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>333.66</v>
+        <v>960.49</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1176812-56-CM26</t>
+          <t>1376-265-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18058,7 +18058,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>960.49</v>
+        <v>333.66</v>
       </c>
     </row>
     <row r="272">
@@ -18194,7 +18194,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3175-56-CM26</t>
+          <t>1376-283-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>732.79</v>
+        <v>987.38</v>
       </c>
     </row>
     <row r="275">
@@ -18324,7 +18324,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1376-283-CM26</t>
+          <t>3175-56-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>987.38</v>
+        <v>732.79</v>
       </c>
     </row>
     <row r="277">
@@ -18649,7 +18649,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3175-64-CM26</t>
+          <t>1376-344-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18669,17 +18669,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>194.82</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1376-344-CM26</t>
+          <t>3175-64-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18734,17 +18734,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,7 +18773,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>121.76</v>
+        <v>194.82</v>
       </c>
     </row>
     <row r="283">
@@ -18974,7 +18974,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1028871-342-CM26</t>
+          <t>873-20-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>161.96</v>
+        <v>219.13</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1028871-341-CM26</t>
+          <t>1028871-342-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>80.98</v>
+        <v>161.96</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>873-20-CM26</t>
+          <t>1028871-341-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19129,12 +19129,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,13 +19163,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>219.13</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1376-381-CM26</t>
+          <t>1376-383-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>196.71</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1376-383-CM26</t>
+          <t>1376-381-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19293,7 +19293,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>107.2</v>
+        <v>196.71</v>
       </c>
     </row>
     <row r="291">
@@ -19494,7 +19494,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2579-22-CM26</t>
+          <t>778993-70-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19534,17 +19534,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -19553,13 +19553,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>130.65</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>778993-70-CM26</t>
+          <t>2579-22-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19584,12 +19584,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19599,17 +19599,17 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>200.16</v>
+        <v>130.65</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1028871-364-CM26</t>
+          <t>1171166-199-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19644,17 +19644,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19683,13 +19683,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>224.17</v>
+        <v>116.71</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1171166-199-CM26</t>
+          <t>1028871-364-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19709,17 +19709,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>116.71</v>
+        <v>224.17</v>
       </c>
     </row>
     <row r="298">
@@ -19884,7 +19884,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1796-28-CM26</t>
+          <t>1376-408-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>23.44</v>
+        <v>1160.18</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1376-408-CM26</t>
+          <t>1796-28-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1160.18</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="302">
@@ -20469,7 +20469,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1376-447-CM26</t>
+          <t>810406-107-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20528,13 +20528,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>116.59</v>
+        <v>163.35</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>810406-107-CM26</t>
+          <t>1376-447-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20559,12 +20559,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20593,13 +20593,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>163.35</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>3175-81-CM26</t>
+          <t>1028871-408-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20624,12 +20624,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.102.143-7</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20639,17 +20639,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -20658,13 +20658,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>175.96</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1028871-408-CM26</t>
+          <t>3175-81-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20689,12 +20689,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.102.143-7</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20704,17 +20704,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -20723,13 +20723,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>71.31</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>778993-91-CM26</t>
+          <t>1556-185-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20754,12 +20754,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20769,17 +20769,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -20788,13 +20788,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>817.79</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1556-185-CM26</t>
+          <t>778993-91-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20834,17 +20834,17 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>159.1</v>
+        <v>817.79</v>
       </c>
     </row>
     <row r="315">
@@ -20924,7 +20924,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1376-459-CM26</t>
+          <t>1079486-137-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20949,12 +20949,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20964,17 +20964,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -20983,13 +20983,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>789.51</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1079486-137-CM26</t>
+          <t>1376-459-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -21014,12 +21014,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -21029,17 +21029,17 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>104.42</v>
+        <v>789.51</v>
       </c>
     </row>
     <row r="318">
@@ -21639,7 +21639,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1376-517-CM26</t>
+          <t>904-117-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21664,12 +21664,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21679,17 +21679,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>796.42</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>904-117-CM26</t>
+          <t>1376-517-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21744,17 +21744,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21763,7 +21763,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>84.67</v>
+        <v>796.42</v>
       </c>
     </row>
     <row r="329">
@@ -21964,7 +21964,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1376-521-CM26</t>
+          <t>3281-59-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22004,17 +22004,17 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>100.23</v>
+        <v>255.74</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>3281-59-CM26</t>
+          <t>1376-521-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22069,17 +22069,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>255.74</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1554-1319-CM26</t>
+          <t>1376-545-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22134,17 +22134,17 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -22153,13 +22153,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1315.87</v>
+        <v>206.78</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1376-545-CM26</t>
+          <t>1554-1319-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22184,12 +22184,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22199,17 +22199,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>206.78</v>
+        <v>1315.87</v>
       </c>
     </row>
     <row r="336">
@@ -22809,7 +22809,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1376-646-CM26</t>
+          <t>1171166-224-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22849,17 +22849,17 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -22868,13 +22868,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>130.25</v>
+        <v>194.45</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1376-645-CM26</t>
+          <t>1079486-205-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22899,12 +22899,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22914,17 +22914,17 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -22933,13 +22933,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>279.1</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1171166-224-CM26</t>
+          <t>1376-646-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22964,12 +22964,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22979,17 +22979,17 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -22998,13 +22998,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>194.45</v>
+        <v>130.25</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1079486-205-CM26</t>
+          <t>1376-645-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23029,12 +23029,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -23044,17 +23044,17 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>101.74</v>
+        <v>279.1</v>
       </c>
     </row>
     <row r="349">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -23589,7 +23589,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1376-705-CM26</t>
+          <t>1376-688-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23609,7 +23609,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -23654,7 +23654,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>778993-144-CM26</t>
+          <t>1376-705-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23679,12 +23679,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23694,17 +23694,17 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>686.17</v>
+        <v>758.89</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1376-688-CM26</t>
+          <t>778993-144-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23739,17 +23739,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>758.89</v>
+        <v>686.17</v>
       </c>
     </row>
     <row r="360">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -23844,6 +23844,331 @@
       </c>
       <c r="M360" s="2" t="n">
         <v>782.55</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1554-1681-CM26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>1368.55</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>3175-133-CM26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>61.102.143-7</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>889.84</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1376-751-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>105.95</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1376-752-CM26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>423.82</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>3175-138-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>61.102.143-7</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>211.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/atacama.xlsx
@@ -20879,7 +20879,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -21269,7 +21269,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -21399,7 +21399,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
